--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.55957</v>
+        <v>16.88646</v>
       </c>
       <c r="D2" t="n">
-        <v>16.39884</v>
+        <v>16.1942</v>
       </c>
       <c r="E2" t="n">
-        <v>16.35732</v>
+        <v>16.87052</v>
       </c>
       <c r="F2" t="n">
-        <v>43.44132</v>
+        <v>42.60301</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05025</v>
+        <v>0.05043</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78352</v>
+        <v>1.8062</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.80746</v>
+        <v>17.02838</v>
       </c>
       <c r="D3" t="n">
-        <v>16.49569</v>
+        <v>16.75407</v>
       </c>
       <c r="E3" t="n">
-        <v>16.22857</v>
+        <v>16.8381</v>
       </c>
       <c r="F3" t="n">
-        <v>42.85153</v>
+        <v>41.94595</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05054</v>
+        <v>0.05164</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79507</v>
+        <v>1.82798</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.43182</v>
+        <v>16.68928</v>
       </c>
       <c r="D4" t="n">
-        <v>16.52243</v>
+        <v>16.63931</v>
       </c>
       <c r="E4" t="n">
-        <v>16.58327</v>
+        <v>16.65007</v>
       </c>
       <c r="F4" t="n">
-        <v>42.93048</v>
+        <v>42.99737</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0497</v>
+        <v>0.04915</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81991</v>
+        <v>1.8059</v>
       </c>
     </row>
   </sheetData>
